--- a/Team-Data/2013-14/1-30-2013-14.xlsx
+++ b/Team-Data/2013-14/1-30-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
@@ -948,7 +1015,7 @@
         <v>25</v>
       </c>
       <c r="AM3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN3" t="n">
         <v>28</v>
@@ -972,16 +1039,16 @@
         <v>17</v>
       </c>
       <c r="AU3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV3" t="n">
         <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -1172,13 +1239,13 @@
         <v>24</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1536,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -1571,34 +1638,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" t="n">
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>0.348</v>
+        <v>0.356</v>
       </c>
       <c r="H7" t="n">
         <v>48.9</v>
       </c>
       <c r="I7" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J7" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="L7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N7" t="n">
         <v>0.361</v>
@@ -1613,55 +1680,55 @@
         <v>0.74</v>
       </c>
       <c r="R7" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S7" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="U7" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="V7" t="n">
         <v>14.7</v>
       </c>
       <c r="W7" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA7" t="n">
         <v>19.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.8</v>
+        <v>-5.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>22</v>
@@ -1673,16 +1740,16 @@
         <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN7" t="n">
         <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
         <v>19</v>
@@ -1700,13 +1767,13 @@
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
@@ -1715,16 +1782,16 @@
         <v>28</v>
       </c>
       <c r="AZ7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA7" t="n">
         <v>21</v>
       </c>
       <c r="BB7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC7" t="n">
         <v>25</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>26</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
@@ -2028,7 +2095,7 @@
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ9" t="n">
         <v>6</v>
@@ -2061,7 +2128,7 @@
         <v>6</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2070,7 +2137,7 @@
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -2195,22 +2262,22 @@
         <v>-3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF10" t="n">
         <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
         <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2366,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11" t="n">
         <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>0.596</v>
+        <v>0.587</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>84.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L11" t="n">
         <v>9.4</v>
       </c>
       <c r="M11" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.383</v>
+        <v>0.385</v>
       </c>
       <c r="O11" t="n">
         <v>16.1</v>
@@ -2341,19 +2408,19 @@
         <v>0.735</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S11" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="T11" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="U11" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V11" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W11" t="n">
         <v>7.8</v>
@@ -2362,22 +2429,22 @@
         <v>5.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z11" t="n">
         <v>22.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.7</v>
+        <v>103.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,10 +2456,10 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
         <v>7</v>
@@ -2407,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
         <v>25</v>
@@ -2440,7 +2507,7 @@
         <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
         <v>25</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2616,7 +2683,7 @@
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" t="n">
         <v>35</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.778</v>
+        <v>0.795</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
@@ -2681,19 +2748,19 @@
         <v>36.8</v>
       </c>
       <c r="J13" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K13" t="n">
         <v>0.455</v>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M13" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.356</v>
+        <v>0.361</v>
       </c>
       <c r="O13" t="n">
         <v>18</v>
@@ -2702,10 +2769,10 @@
         <v>23.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R13" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S13" t="n">
         <v>35.2</v>
@@ -2714,13 +2781,13 @@
         <v>45.4</v>
       </c>
       <c r="U13" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="V13" t="n">
         <v>15.2</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X13" t="n">
         <v>5.7</v>
@@ -2735,13 +2802,13 @@
         <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2750,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
@@ -2765,13 +2832,13 @@
         <v>11</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
         <v>12</v>
@@ -2783,13 +2850,13 @@
         <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU13" t="n">
         <v>19</v>
@@ -2798,7 +2865,7 @@
         <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -2845,28 +2912,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" t="n">
         <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.673</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="J14" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>0.468</v>
+        <v>0.469</v>
       </c>
       <c r="L14" t="n">
         <v>8.300000000000001</v>
@@ -2881,46 +2948,46 @@
         <v>21</v>
       </c>
       <c r="P14" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.73</v>
+        <v>0.732</v>
       </c>
       <c r="R14" t="n">
         <v>10.2</v>
       </c>
       <c r="S14" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T14" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y14" t="n">
         <v>3.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>106</v>
+        <v>106.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2935,10 +3002,10 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2965,13 +3032,13 @@
         <v>24</v>
       </c>
       <c r="AR14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
         <v>14</v>
       </c>
       <c r="AT14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -2980,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
         <v>19</v>
@@ -2995,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>-5.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH15" t="n">
         <v>26</v>
@@ -3126,7 +3193,7 @@
         <v>11</v>
       </c>
       <c r="AK15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3168,7 +3235,7 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
         <v>11</v>
@@ -3180,7 +3247,7 @@
         <v>15</v>
       </c>
       <c r="BC15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3359,7 +3426,7 @@
         <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>6</v>
@@ -3484,7 +3551,7 @@
         <v>9</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3499,7 +3566,7 @@
         <v>14</v>
       </c>
       <c r="AN17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO17" t="n">
         <v>13</v>
@@ -3508,7 +3575,7 @@
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3675,7 +3742,7 @@
         <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="n">
         <v>16</v>
@@ -3684,10 +3751,10 @@
         <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ18" t="n">
         <v>18</v>
@@ -3696,7 +3763,7 @@
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>4.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>13</v>
@@ -3845,7 +3912,7 @@
         <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>9</v>
@@ -3905,7 +3972,7 @@
         <v>3</v>
       </c>
       <c r="BB19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4063,7 +4130,7 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU20" t="n">
         <v>15</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -4119,88 +4186,88 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F21" t="n">
         <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.413</v>
+        <v>0.4</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J21" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.442</v>
+        <v>0.439</v>
       </c>
       <c r="L21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M21" t="n">
         <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>0.366</v>
+        <v>0.364</v>
       </c>
       <c r="O21" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P21" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U21" t="n">
         <v>20.4</v>
       </c>
       <c r="V21" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W21" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X21" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>97</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.8</v>
+        <v>-2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
         <v>20</v>
@@ -4209,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4218,7 +4285,7 @@
         <v>14</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4230,13 +4297,13 @@
         <v>13</v>
       </c>
       <c r="AO21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4248,7 +4315,7 @@
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4257,13 +4324,13 @@
         <v>12</v>
       </c>
       <c r="AX21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY21" t="n">
         <v>5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA21" t="n">
         <v>22</v>
@@ -4272,7 +4339,7 @@
         <v>22</v>
       </c>
       <c r="BC21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -4385,16 +4452,16 @@
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
         <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ22" t="n">
         <v>16</v>
@@ -4436,7 +4503,7 @@
         <v>26</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4649,7 @@
         <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>18</v>
@@ -4600,7 +4667,7 @@
         <v>21</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
@@ -4612,7 +4679,7 @@
         <v>22</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>17</v>
@@ -4627,13 +4694,13 @@
         <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>27</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>26</v>
@@ -4764,7 +4831,7 @@
         <v>2</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F25" t="n">
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.609</v>
+        <v>0.6</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,37 +4932,37 @@
         <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L25" t="n">
         <v>9.4</v>
       </c>
       <c r="M25" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O25" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P25" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R25" t="n">
         <v>11.7</v>
       </c>
       <c r="S25" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T25" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U25" t="n">
         <v>19.4</v>
@@ -4919,13 +4986,13 @@
         <v>21.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.9</v>
+        <v>105</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
         <v>8</v>
@@ -4937,7 +5004,7 @@
         <v>8</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
         <v>8</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
         <v>11</v>
@@ -4964,7 +5031,7 @@
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
@@ -4994,7 +5061,7 @@
         <v>22</v>
       </c>
       <c r="BA25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO26" t="n">
         <v>9</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5716,10 +5783,10 @@
         <v>23</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA29" t="n">
         <v>6</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -5847,7 +5914,7 @@
         <v>23</v>
       </c>
       <c r="AH30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
@@ -5856,7 +5923,7 @@
         <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
         <v>22</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-30-2013-14</t>
+          <t>2014-01-30</t>
         </is>
       </c>
     </row>
